--- a/results/2021-06-01_to_2022-06-01/Performance_Summary.xlsx
+++ b/results/2021-06-01_to_2022-06-01/Performance_Summary.xlsx
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.6129802797333136</v>
+        <v>-3.23330811525385</v>
       </c>
       <c r="C4" t="n">
-        <v>19.14641550746893</v>
+        <v>19.50129324484565</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03201540672164943</v>
+        <v>-0.1657996767013613</v>
       </c>
       <c r="E4" t="n">
-        <v>-18.49490649878358</v>
+        <v>-19.4130779722995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8412626160764151</v>
+        <v>0.9656126475796927</v>
       </c>
     </row>
     <row r="5">
